--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
@@ -919,7 +919,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2001</t>
         </is>
       </c>
       <c r="G3" s="46" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="AA-FR-003" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +12,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AA-FR-003'!$A$1:$I$42</definedName>
   </definedNames>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,13 +88,6 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -116,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -140,19 +133,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -174,17 +154,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -260,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -298,98 +267,71 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,67 +808,68 @@
     <col width="15.42578125" customWidth="1" style="1" min="7" max="7"/>
     <col width="11.140625" customWidth="1" style="1" min="8" max="8"/>
     <col width="11.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="11.42578125" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="1" min="10" max="10"/>
+    <col width="11.42578125" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customFormat="1" customHeight="1" s="3">
-      <c r="A1" s="17" t="n"/>
-      <c r="B1" s="40" t="n"/>
-      <c r="C1" s="15" t="inlineStr">
+    <row r="1" ht="30.75" customFormat="1" customHeight="1" s="33">
+      <c r="A1" s="22" t="n"/>
+      <c r="B1" s="23" t="n"/>
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>FORMATO DE SYLLABUS</t>
         </is>
       </c>
-      <c r="D1" s="41" t="n"/>
-      <c r="E1" s="42" t="n"/>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Código: AA-FR-003</t>
         </is>
       </c>
-      <c r="G1" s="16" t="n"/>
-      <c r="H1" s="43" t="n"/>
-      <c r="I1" s="40" t="n"/>
-    </row>
-    <row r="2" ht="27.95" customFormat="1" customHeight="1" s="3">
-      <c r="A2" s="44" t="n"/>
-      <c r="B2" s="45" t="n"/>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="32" t="n"/>
+      <c r="I1" s="23" t="n"/>
+    </row>
+    <row r="2" ht="27.95" customFormat="1" customHeight="1" s="33">
+      <c r="A2" s="24" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>Macroproceso: Direccionamiento Estratégico</t>
         </is>
       </c>
-      <c r="D2" s="41" t="n"/>
-      <c r="E2" s="42" t="n"/>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="29" t="inlineStr">
         <is>
           <t>Versión: 02</t>
         </is>
       </c>
-      <c r="G2" s="44" t="n"/>
-      <c r="I2" s="45" t="n"/>
-    </row>
-    <row r="3" ht="48.95" customFormat="1" customHeight="1" s="3">
-      <c r="A3" s="46" t="n"/>
-      <c r="B3" s="47" t="n"/>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="G2" s="24" t="n"/>
+      <c r="I2" s="25" t="n"/>
+    </row>
+    <row r="3" ht="48.95" customFormat="1" customHeight="1" s="33">
+      <c r="A3" s="26" t="n"/>
+      <c r="B3" s="27" t="n"/>
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Proceso: Autoevaluación y Acreditación</t>
         </is>
       </c>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="42" t="n"/>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2001</t>
-        </is>
-      </c>
-      <c r="G3" s="46" t="n"/>
-      <c r="H3" s="48" t="n"/>
-      <c r="I3" s="47" t="n"/>
-    </row>
-    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="2">
+15/15/2015</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="27" t="n"/>
+    </row>
+    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="31">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -937,286 +880,286 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
     </row>
-    <row r="5" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="27" t="inlineStr">
+    <row r="5" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">FACULTAD: </t>
         </is>
       </c>
-      <c r="B5" s="42" t="n"/>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Tecnológica</t>
         </is>
       </c>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="41" t="n"/>
-      <c r="H5" s="41" t="n"/>
-      <c r="I5" s="42" t="n"/>
-    </row>
-    <row r="6" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>PROYECTO CURRICULAR:</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n"/>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Tecnología en Electrónica Industrial</t>
         </is>
       </c>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="42" t="n"/>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>CÓDIGO PLAN DE ESTUDIOS:</t>
         </is>
       </c>
-      <c r="H6" s="42" t="n"/>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="7" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>I. IDENTIFICACIÓN DEL ESPACIO ACADÉMICO</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="41" t="n"/>
-      <c r="H7" s="41" t="n"/>
-      <c r="I7" s="42" t="n"/>
-    </row>
-    <row r="8" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>NOMBRE DEL ESPACIO ACADÉMICO:  Producción y Comprensión de Textos II</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n"/>
-      <c r="D8" s="41" t="n"/>
-      <c r="E8" s="41" t="n"/>
-      <c r="F8" s="41" t="n"/>
-      <c r="G8" s="41" t="n"/>
-      <c r="H8" s="41" t="n"/>
-      <c r="I8" s="42" t="n"/>
-    </row>
-    <row r="9" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Código del espacio académico:</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="42" t="n"/>
-      <c r="D9" s="28" t="n">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="18" t="n">
         <v>1056</v>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>Número de créditos académicos:</t>
         </is>
       </c>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="42" t="n"/>
-      <c r="H9" s="28" t="n">
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="42" t="n"/>
-    </row>
-    <row r="10" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="I9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Distribución horas de trabajo:</t>
         </is>
       </c>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="42" t="n"/>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>HTD</t>
         </is>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>HTC</t>
         </is>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="28" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>HTA</t>
         </is>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A11" s="18" t="inlineStr">
+    <row r="11" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Tipo de espacio académico:</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="42" t="n"/>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>Cátedra</t>
         </is>
       </c>
       <c r="G11" s="10" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="H11" s="40" t="n"/>
+      <c r="I11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>NATURALEZA DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n"/>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
-      <c r="F12" s="41" t="n"/>
-      <c r="G12" s="41" t="n"/>
-      <c r="H12" s="41" t="n"/>
-      <c r="I12" s="42" t="n"/>
-    </row>
-    <row r="13" ht="32.1" customFormat="1" customHeight="1" s="2">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="32.1" customFormat="1" customHeight="1" s="31">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Obligatorio
  Básico</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Obligatorio
 Complementario</t>
         </is>
       </c>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>Electivo Intrínseco</t>
         </is>
       </c>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="40" t="inlineStr">
         <is>
           <t>Electivo Extrínseco</t>
         </is>
       </c>
       <c r="I13" s="10" t="n"/>
     </row>
-    <row r="14" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="21" t="inlineStr">
+    <row r="14" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>CARÁCTER DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n"/>
-      <c r="D14" s="41" t="n"/>
-      <c r="E14" s="41" t="n"/>
-      <c r="F14" s="41" t="n"/>
-      <c r="G14" s="41" t="n"/>
-      <c r="H14" s="41" t="n"/>
-      <c r="I14" s="42" t="n"/>
-    </row>
-    <row r="15" ht="30.95" customFormat="1" customHeight="1" s="2">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="30.95" customFormat="1" customHeight="1" s="31">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Teórico</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Práctico</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>Teórico-Práctico</t>
         </is>
       </c>
-      <c r="F15" s="22" t="n"/>
+      <c r="F15" s="40" t="n"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Otros:</t>
         </is>
       </c>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>Cuál:_______</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A16" s="21" t="inlineStr">
+    <row r="16" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>MODALIDAD DE OFERTA DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B16" s="41" t="n"/>
-      <c r="C16" s="41" t="n"/>
-      <c r="D16" s="41" t="n"/>
-      <c r="E16" s="41" t="n"/>
-      <c r="F16" s="41" t="n"/>
-      <c r="G16" s="41" t="n"/>
-      <c r="H16" s="41" t="n"/>
-      <c r="I16" s="42" t="n"/>
-    </row>
-    <row r="17" ht="32.1" customFormat="1" customHeight="1" s="2">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="32.1" customFormat="1" customHeight="1" s="31">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Presencial con incorporación de TIC</t>
         </is>
@@ -1228,95 +1171,95 @@
         </is>
       </c>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="37" t="inlineStr">
         <is>
           <t>Otros:</t>
         </is>
       </c>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I17" s="37" t="inlineStr">
         <is>
           <t>Cuál:_______</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>II.  SUGERENCIAS DE SABERES Y CONOCIMIENTOS PREVIOS</t>
         </is>
       </c>
-      <c r="B18" s="41" t="n"/>
-      <c r="C18" s="41" t="n"/>
-      <c r="D18" s="41" t="n"/>
-      <c r="E18" s="41" t="n"/>
-      <c r="F18" s="41" t="n"/>
-      <c r="G18" s="41" t="n"/>
-      <c r="H18" s="41" t="n"/>
-      <c r="I18" s="42" t="n"/>
-    </row>
-    <row r="19" ht="48" customFormat="1" customHeight="1" s="2">
-      <c r="A19" s="49" t="inlineStr">
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="48" customFormat="1" customHeight="1" s="31">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Es recomendable que el estudiante haya cursado la asignatura Producción y Comprensión de Textos I. Debe contar con nociones básicas sobre redacción, comprensión lectora, citación bibliográfica y estructura del texto académico. Se valorará el interés por la comunicación clara, el pensamiento estructurado y el trabajo autónomo en la escritura de textos. </t>
         </is>
       </c>
-      <c r="B19" s="41" t="n"/>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="41" t="n"/>
-      <c r="G19" s="41" t="n"/>
-      <c r="H19" s="41" t="n"/>
-      <c r="I19" s="42" t="n"/>
-    </row>
-    <row r="20" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>III. JUSTIFICACIÓN DEL ESPACIO ACADÉMICO</t>
         </is>
       </c>
-      <c r="B20" s="41" t="n"/>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
-      <c r="F20" s="41" t="n"/>
-      <c r="G20" s="41" t="n"/>
-      <c r="H20" s="41" t="n"/>
-      <c r="I20" s="42" t="n"/>
-    </row>
-    <row r="21" ht="66" customFormat="1" customHeight="1" s="2">
-      <c r="A21" s="49" t="inlineStr">
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="66" customFormat="1" customHeight="1" s="31">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> La claridad comunicativa es una competencia transversal esencial para los profesionales técnicos. En campos como la ciencia, la ingeniería o la tecnología, la redacción de textos científicos y técnicos exige el dominio de estructuras, registros y criterios discursivos específicos. Esta asignatura refuerza las habilidades lingüísticas, argumentativas y estructurales para producir textos académicos y profesionales con rigor, sentido crítico y ética informacional, en escenarios de creciente digitalización, innovación e interdisciplina. </t>
         </is>
       </c>
-      <c r="B21" s="41" t="n"/>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="41" t="n"/>
-      <c r="G21" s="41" t="n"/>
-      <c r="H21" s="41" t="n"/>
-      <c r="I21" s="42" t="n"/>
-    </row>
-    <row r="22" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>IV. OBJETIVOS DEL ESPACIO ACADÉMICO (GENERAL Y ESPECÍFICOS)</t>
         </is>
       </c>
-      <c r="B22" s="41" t="n"/>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="41" t="n"/>
-      <c r="F22" s="41" t="n"/>
-      <c r="G22" s="41" t="n"/>
-      <c r="H22" s="41" t="n"/>
-      <c r="I22" s="42" t="n"/>
-    </row>
-    <row r="23" ht="180" customFormat="1" customHeight="1" s="2">
-      <c r="A23" s="49" t="inlineStr">
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="180" customFormat="1" customHeight="1" s="31">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo General 
 Fortalecer en el estudiante las competencias comunicativas necesarias para la comprensión y producción de textos científicos, técnicos y argumentativos, mediante el análisis crítico, la apropiación de estructuras textuales y el uso ético de la información. 
@@ -1328,32 +1271,32 @@
 •	Fortalecer la argumentación escrita mediante distintos modos de razonamiento lógico y crítico. </t>
         </is>
       </c>
-      <c r="B23" s="41" t="n"/>
-      <c r="C23" s="41" t="n"/>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="41" t="n"/>
-      <c r="F23" s="41" t="n"/>
-      <c r="G23" s="41" t="n"/>
-      <c r="H23" s="41" t="n"/>
-      <c r="I23" s="42" t="n"/>
-    </row>
-    <row r="24" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">V. PROPÓSITOS DE FORMACIÓN Y DE APRENDIZAJE (PFA) DEL ESPACIO ACADÉMICO </t>
         </is>
       </c>
-      <c r="B24" s="41" t="n"/>
-      <c r="C24" s="41" t="n"/>
-      <c r="D24" s="41" t="n"/>
-      <c r="E24" s="41" t="n"/>
-      <c r="F24" s="41" t="n"/>
-      <c r="G24" s="41" t="n"/>
-      <c r="H24" s="41" t="n"/>
-      <c r="I24" s="42" t="n"/>
-    </row>
-    <row r="25" ht="193.5" customFormat="1" customHeight="1" s="2">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="193.5" customFormat="1" customHeight="1" s="31">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Propósitos de Formación 
 Desarrollar una conciencia crítica y ética sobre la producción y uso del conocimiento científico. 
@@ -1368,32 +1311,32 @@
 Adaptabilidad e innovación. </t>
         </is>
       </c>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="41" t="n"/>
-      <c r="D25" s="41" t="n"/>
-      <c r="E25" s="41" t="n"/>
-      <c r="F25" s="41" t="n"/>
-      <c r="G25" s="41" t="n"/>
-      <c r="H25" s="41" t="n"/>
-      <c r="I25" s="42" t="n"/>
-    </row>
-    <row r="26" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>VI.  CONTENIDOS TEMÁTICOS</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="41" t="n"/>
-      <c r="E26" s="41" t="n"/>
-      <c r="F26" s="41" t="n"/>
-      <c r="G26" s="41" t="n"/>
-      <c r="H26" s="41" t="n"/>
-      <c r="I26" s="42" t="n"/>
-    </row>
-    <row r="27" ht="409.6" customFormat="1" customHeight="1" s="2">
-      <c r="A27" s="49" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="409.6" customFormat="1" customHeight="1" s="31">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Fundamentos para la producción de textos académicos (2 semanas) 
 •	¿Qué es escribir como científico? 
@@ -1426,73 +1369,73 @@
 •	Publicación en repositorio del aula. </t>
         </is>
       </c>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="43" t="n"/>
-      <c r="E27" s="43" t="n"/>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="43" t="n"/>
-      <c r="H27" s="43" t="n"/>
-      <c r="I27" s="40" t="n"/>
-    </row>
-    <row r="28" ht="55.5" customFormat="1" customHeight="1" s="2">
-      <c r="A28" s="46" t="n"/>
-      <c r="B28" s="48" t="n"/>
-      <c r="C28" s="48" t="n"/>
-      <c r="D28" s="48" t="n"/>
-      <c r="E28" s="48" t="n"/>
-      <c r="F28" s="48" t="n"/>
-      <c r="G28" s="48" t="n"/>
-      <c r="H28" s="48" t="n"/>
-      <c r="I28" s="47" t="n"/>
-    </row>
-    <row r="29" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="55.5" customFormat="1" customHeight="1" s="31">
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="34" t="n"/>
+      <c r="D28" s="34" t="n"/>
+      <c r="E28" s="34" t="n"/>
+      <c r="F28" s="34" t="n"/>
+      <c r="G28" s="34" t="n"/>
+      <c r="H28" s="34" t="n"/>
+      <c r="I28" s="27" t="n"/>
+    </row>
+    <row r="29" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>VII. ESTRATEGIAS DE ENSEÑANZA QUE FAVORECEN EL APRENDIZAJE</t>
         </is>
       </c>
-      <c r="B29" s="41" t="n"/>
-      <c r="C29" s="41" t="n"/>
-      <c r="D29" s="41" t="n"/>
-      <c r="E29" s="41" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="41" t="n"/>
-      <c r="I29" s="42" t="n"/>
-    </row>
-    <row r="30" ht="57.75" customFormat="1" customHeight="1" s="2">
-      <c r="A30" s="49" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="57.75" customFormat="1" customHeight="1" s="31">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">La asignatura se desarrollará a través de talleres prácticos, análisis de modelos textuales, escritura guiada, debates argumentativos, corrección entre pares y proyectos finales. Se promoverá la autonomía, el uso de herramientas digitales para la producción textual y la participación activa en ejercicios de escritura académica. </t>
         </is>
       </c>
-      <c r="B30" s="41" t="n"/>
-      <c r="C30" s="41" t="n"/>
-      <c r="D30" s="41" t="n"/>
-      <c r="E30" s="41" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="41" t="n"/>
-      <c r="H30" s="41" t="n"/>
-      <c r="I30" s="42" t="n"/>
-    </row>
-    <row r="31" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>VIII.  EVALUACIÓN</t>
         </is>
       </c>
-      <c r="B31" s="41" t="n"/>
-      <c r="C31" s="41" t="n"/>
-      <c r="D31" s="41" t="n"/>
-      <c r="E31" s="41" t="n"/>
-      <c r="F31" s="41" t="n"/>
-      <c r="G31" s="41" t="n"/>
-      <c r="H31" s="41" t="n"/>
-      <c r="I31" s="42" t="n"/>
-    </row>
-    <row r="32" ht="264.75" customFormat="1" customHeight="1" s="2">
-      <c r="A32" s="49" t="inlineStr">
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="264.75" customFormat="1" customHeight="1" s="31">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> De acuerdo con el estatuto estudiantil vigente (Acuerdo No. 027 de 1993 expedido por el Consejo Superior Universitario y en su Artículo No. 42 y al Artículo No. 3, Literal d) el profesor al presentar el programa presenta una propuesta de evaluación como parte de su propuesta metodológica.  
 Para dar cumplimiento a lo dispuesto en el estatuto estudiantil, los porcentajes por corte se definen como se indica a continuación, con base en las fechas establecidos por el Consejo Académico en el respectivo calendario académico. 
@@ -1502,93 +1445,93 @@
 En todo caso, la evaluación será continua e integral, teniendo en cuenta los avances del estudiante en los siguientes aspectos: i) comprensión conceptual (pruebas escritas, talleres); ii) aplicación práctica (laboratorios, informes técnicos); iii) proyecto integrador final (análisis, diseño, montaje y presentación); y iv) participación y trabajo en equipo. Asimismo, se debe valorar el desarrollo de competencias comunicativas, resolución de problemas, uso de instrumentos, pensamiento lógico y creatividad. Las pruebas se concertarán con el grupo y se ajustarán a las fechas establecidas en el respectivo calendario académico </t>
         </is>
       </c>
-      <c r="B32" s="41" t="n"/>
-      <c r="C32" s="41" t="n"/>
-      <c r="D32" s="41" t="n"/>
-      <c r="E32" s="41" t="n"/>
-      <c r="F32" s="41" t="n"/>
-      <c r="G32" s="41" t="n"/>
-      <c r="H32" s="41" t="n"/>
-      <c r="I32" s="42" t="n"/>
-    </row>
-    <row r="33" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="B32" s="14" t="n"/>
+      <c r="C32" s="14" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>IX. MEDIOS Y RECURSOS EDUCATIVOS</t>
         </is>
       </c>
-      <c r="B33" s="41" t="n"/>
-      <c r="C33" s="41" t="n"/>
-      <c r="D33" s="41" t="n"/>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="41" t="n"/>
-      <c r="G33" s="41" t="n"/>
-      <c r="H33" s="41" t="n"/>
-      <c r="I33" s="42" t="n"/>
-    </row>
-    <row r="34" ht="184.5" customFormat="1" customHeight="1" s="2">
-      <c r="A34" s="49" t="inlineStr">
+      <c r="B33" s="14" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="184.5" customFormat="1" customHeight="1" s="31">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Para el adecuado desarrollo de este espacio académico, se requiere el uso de medios institucionales y recursos individuales que faciliten los procesos de enseñanza y aprendizaje, tanto en ambientes presenciales como virtuales. Las actividades teóricas se apoyarán en aulas de clase dotadas de medios audiovisuales (tablero, videobeam, sillas) y plataformas virtuales institucionales como Microsoft Teams o Google Meet. Además, será fundamental el acceso a presentaciones digitales, textos base, hojas de datos, artículos técnicos, bibliotecas y herramientas digitales (Google Docs, Canva, Moodle, Miro). Se fomentará el uso de gestores de referencias bibliográficas (Zotero, Mendeley). 
 Como recursos propios, el estudiante debe disponer de una calculadora científica, conexión estable a internet que la universidad proporciona, un sistema para la toma de apuntes (cuaderno, tablet o computador) y acceso a los materiales de clase. Será responsabilidad del estudiante descargar los insumos digitales y contar con los elementos necesarios que serán especificados previamente en cada práctica o proyecto. </t>
         </is>
       </c>
-      <c r="B34" s="41" t="n"/>
-      <c r="C34" s="41" t="n"/>
-      <c r="D34" s="41" t="n"/>
-      <c r="E34" s="41" t="n"/>
-      <c r="F34" s="41" t="n"/>
-      <c r="G34" s="41" t="n"/>
-      <c r="H34" s="41" t="n"/>
-      <c r="I34" s="42" t="n"/>
-    </row>
-    <row r="35" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>X. PRÁCTICAS ACADÉMICAS - SALIDAS DE CAMPO</t>
         </is>
       </c>
-      <c r="B35" s="41" t="n"/>
-      <c r="C35" s="41" t="n"/>
-      <c r="D35" s="41" t="n"/>
-      <c r="E35" s="41" t="n"/>
-      <c r="F35" s="41" t="n"/>
-      <c r="G35" s="41" t="n"/>
-      <c r="H35" s="41" t="n"/>
-      <c r="I35" s="42" t="n"/>
-    </row>
-    <row r="36" ht="63.75" customFormat="1" customHeight="1" s="2">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="63.75" customFormat="1" customHeight="1" s="31">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Podrán incluirse actividades como observación de exposiciones científicas, conversatorios con investigadores, participación en ferias académicas, o análisis de informes técnicos reales de empresas o instituciones. Estas prácticas buscan acercar al estudiante a contextos reales de producción de conocimiento. </t>
         </is>
       </c>
-      <c r="B36" s="41" t="n"/>
-      <c r="C36" s="41" t="n"/>
-      <c r="D36" s="41" t="n"/>
-      <c r="E36" s="41" t="n"/>
-      <c r="F36" s="41" t="n"/>
-      <c r="G36" s="41" t="n"/>
-      <c r="H36" s="41" t="n"/>
-      <c r="I36" s="42" t="n"/>
-    </row>
-    <row r="37" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>XI.  BIBLIOGRAFÍA</t>
         </is>
       </c>
-      <c r="B37" s="41" t="n"/>
-      <c r="C37" s="41" t="n"/>
-      <c r="D37" s="41" t="n"/>
-      <c r="E37" s="41" t="n"/>
-      <c r="F37" s="41" t="n"/>
-      <c r="G37" s="41" t="n"/>
-      <c r="H37" s="41" t="n"/>
-      <c r="I37" s="42" t="n"/>
-    </row>
-    <row r="38" ht="72" customFormat="1" customHeight="1" s="2">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="72" customFormat="1" customHeight="1" s="31">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">•	Cassany, D. (2006). La cocina de la escritura. Anagrama. 
 •	Eco, U. (2001). Cómo se hace una tesis. Gedisa. 
@@ -1596,66 +1539,66 @@
 •	Swales, J. &amp; Feak, C. (2012). Academic Writing for Graduate Students. University of Michigan Press. </t>
         </is>
       </c>
-      <c r="B38" s="41" t="n"/>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="41" t="n"/>
-      <c r="I38" s="42" t="n"/>
-    </row>
-    <row r="39" ht="21.95" customFormat="1" customHeight="1" s="2">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="B38" s="14" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="21.95" customFormat="1" customHeight="1" s="31">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>XII. SEGUIMIENTO Y ACTUALIZACIÓN DEL SYLLABUS</t>
         </is>
       </c>
-      <c r="B39" s="41" t="n"/>
-      <c r="C39" s="41" t="n"/>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="41" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="41" t="n"/>
-      <c r="H39" s="41" t="n"/>
-      <c r="I39" s="42" t="n"/>
-    </row>
-    <row r="40" customFormat="1" s="2">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="15" t="n"/>
+    </row>
+    <row r="40" customFormat="1" s="31">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>Fecha revisión por Consejo Curricular:</t>
         </is>
       </c>
-      <c r="B40" s="41" t="n"/>
-      <c r="C40" s="42" t="n"/>
-      <c r="D40" s="28" t="n"/>
-      <c r="E40" s="41" t="n"/>
-      <c r="F40" s="41" t="n"/>
-      <c r="G40" s="41" t="n"/>
-      <c r="H40" s="41" t="n"/>
-      <c r="I40" s="42" t="n"/>
-    </row>
-    <row r="41" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="B40" s="14" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="30" customFormat="1" customHeight="1" s="31">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Fecha aprobación por Consejo Curricular:</t>
         </is>
       </c>
-      <c r="B41" s="28" t="n"/>
-      <c r="C41" s="28" t="n"/>
-      <c r="D41" s="28" t="n"/>
-      <c r="E41" s="41" t="n"/>
-      <c r="F41" s="42" t="n"/>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="40" t="inlineStr">
         <is>
           <t>Número de acta:</t>
         </is>
       </c>
-      <c r="H41" s="28" t="n"/>
-      <c r="I41" s="42" t="n"/>
-    </row>
-    <row r="42" ht="6" customFormat="1" customHeight="1" s="2">
-      <c r="A42" s="23" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="6" customFormat="1" customHeight="1" s="31">
+      <c r="A42" s="30" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -1669,9 +1612,9 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A33:I33"/>
@@ -1679,8 +1622,8 @@
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="C6:F6"/>
+    <mergeCell ref="G1:I3"/>
     <mergeCell ref="A23:I23"/>
-    <mergeCell ref="G1:I3"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A22:I22"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="AA-FR-003" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,14 +12,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'AA-FR-003'!$A$1:$I$42</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -109,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -133,6 +140,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -154,6 +174,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -229,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -267,71 +298,98 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -808,68 +866,67 @@
     <col width="15.42578125" customWidth="1" style="1" min="7" max="7"/>
     <col width="11.140625" customWidth="1" style="1" min="8" max="8"/>
     <col width="11.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="11.42578125" customWidth="1" style="1" min="10" max="10"/>
-    <col width="11.42578125" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="11.42578125" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customFormat="1" customHeight="1" s="33">
-      <c r="A1" s="22" t="n"/>
-      <c r="B1" s="23" t="n"/>
-      <c r="C1" s="17" t="inlineStr">
+    <row r="1" ht="30.75" customFormat="1" customHeight="1" s="3">
+      <c r="A1" s="17" t="n"/>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>FORMATO DE SYLLABUS</t>
         </is>
       </c>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="D1" s="41" t="n"/>
+      <c r="E1" s="42" t="n"/>
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Código: AA-FR-003</t>
         </is>
       </c>
-      <c r="G1" s="29" t="n"/>
-      <c r="H1" s="32" t="n"/>
-      <c r="I1" s="23" t="n"/>
-    </row>
-    <row r="2" ht="27.95" customFormat="1" customHeight="1" s="33">
-      <c r="A2" s="24" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="G1" s="16" t="n"/>
+      <c r="H1" s="43" t="n"/>
+      <c r="I1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="27.95" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="44" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Macroproceso: Direccionamiento Estratégico</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="D2" s="41" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Versión: 02</t>
         </is>
       </c>
-      <c r="G2" s="24" t="n"/>
-      <c r="I2" s="25" t="n"/>
-    </row>
-    <row r="3" ht="48.95" customFormat="1" customHeight="1" s="33">
-      <c r="A3" s="26" t="n"/>
-      <c r="B3" s="27" t="n"/>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="G2" s="44" t="n"/>
+      <c r="I2" s="45" t="n"/>
+    </row>
+    <row r="3" ht="48.95" customFormat="1" customHeight="1" s="3">
+      <c r="A3" s="46" t="n"/>
+      <c r="B3" s="47" t="n"/>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Proceso: Autoevaluación y Acreditación</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="D3" s="41" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-15/15/2015</t>
-        </is>
-      </c>
-      <c r="G3" s="26" t="n"/>
-      <c r="H3" s="34" t="n"/>
-      <c r="I3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="31">
+22/02/2025</t>
+        </is>
+      </c>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="48" t="n"/>
+      <c r="I3" s="47" t="n"/>
+    </row>
+    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="2">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -880,286 +937,286 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
     </row>
-    <row r="5" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A5" s="38" t="inlineStr">
+    <row r="5" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">FACULTAD: </t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Tecnológica</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="15" t="n"/>
-    </row>
-    <row r="6" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="41" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="G5" s="41" t="n"/>
+      <c r="H5" s="41" t="n"/>
+      <c r="I5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>PROYECTO CURRICULAR:</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="B6" s="42" t="n"/>
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Tecnología en Electrónica Industrial</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="36" t="inlineStr">
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="41" t="n"/>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>CÓDIGO PLAN DE ESTUDIOS:</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n"/>
+      <c r="H6" s="42" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>I. IDENTIFICACIÓN DEL ESPACIO ACADÉMICO</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="n"/>
-      <c r="I7" s="15" t="n"/>
-    </row>
-    <row r="8" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="41" t="n"/>
+      <c r="F7" s="41" t="n"/>
+      <c r="G7" s="41" t="n"/>
+      <c r="H7" s="41" t="n"/>
+      <c r="I7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>NOMBRE DEL ESPACIO ACADÉMICO:  Producción y Comprensión de Textos II</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="15" t="n"/>
-    </row>
-    <row r="9" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="B8" s="41" t="n"/>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="41" t="n"/>
+      <c r="E8" s="41" t="n"/>
+      <c r="F8" s="41" t="n"/>
+      <c r="G8" s="41" t="n"/>
+      <c r="H8" s="41" t="n"/>
+      <c r="I8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Código del espacio académico:</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="18" t="n">
+      <c r="B9" s="41" t="n"/>
+      <c r="C9" s="42" t="n"/>
+      <c r="D9" s="28" t="n">
         <v>1056</v>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>Número de créditos académicos:</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="18" t="n">
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="15" t="n"/>
-    </row>
-    <row r="10" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="I9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Distribución horas de trabajo:</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="B10" s="41" t="n"/>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>HTD</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>HTC</t>
         </is>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>HTA</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="I10" s="28" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A11" s="37" t="inlineStr">
+    <row r="11" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Tipo de espacio académico:</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="42" t="n"/>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Asignatura</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F11" s="40" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Cátedra</t>
         </is>
       </c>
       <c r="G11" s="10" t="n"/>
-      <c r="H11" s="40" t="n"/>
-      <c r="I11" s="18" t="n"/>
-    </row>
-    <row r="12" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>NATURALEZA DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="15" t="n"/>
-    </row>
-    <row r="13" ht="32.1" customFormat="1" customHeight="1" s="31">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="32.1" customFormat="1" customHeight="1" s="2">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Obligatorio
  Básico</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Obligatorio
 Complementario</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F13" s="40" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>Electivo Intrínseco</t>
         </is>
       </c>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="40" t="inlineStr">
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>Electivo Extrínseco</t>
         </is>
       </c>
       <c r="I13" s="10" t="n"/>
     </row>
-    <row r="14" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="14" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>CARÁCTER DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="30.95" customFormat="1" customHeight="1" s="31">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="G14" s="41" t="n"/>
+      <c r="H14" s="41" t="n"/>
+      <c r="I14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="30.95" customFormat="1" customHeight="1" s="2">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Teórico</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Práctico</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>Teórico-Práctico</t>
         </is>
       </c>
-      <c r="F15" s="40" t="n"/>
+      <c r="F15" s="22" t="n"/>
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Otros:</t>
         </is>
       </c>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="37" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>Cuál:_______</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="16" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>MODALIDAD DE OFERTA DEL ESPACIO ACADÉMICO:</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="32.1" customFormat="1" customHeight="1" s="31">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
+      <c r="F16" s="41" t="n"/>
+      <c r="G16" s="41" t="n"/>
+      <c r="H16" s="41" t="n"/>
+      <c r="I16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="32.1" customFormat="1" customHeight="1" s="2">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Presencial</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Presencial con incorporación de TIC</t>
         </is>
@@ -1171,95 +1228,95 @@
         </is>
       </c>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="37" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>Otros:</t>
         </is>
       </c>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="37" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>Cuál:_______</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A18" s="20" t="inlineStr">
+    <row r="18" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>II.  SUGERENCIAS DE SABERES Y CONOCIMIENTOS PREVIOS</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="48" customFormat="1" customHeight="1" s="31">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B18" s="41" t="n"/>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="G18" s="41" t="n"/>
+      <c r="H18" s="41" t="n"/>
+      <c r="I18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="48" customFormat="1" customHeight="1" s="2">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Es recomendable que el estudiante haya cursado la asignatura Producción y Comprensión de Textos I. Debe contar con nociones básicas sobre redacción, comprensión lectora, citación bibliográfica y estructura del texto académico. Se valorará el interés por la comunicación clara, el pensamiento estructurado y el trabajo autónomo en la escritura de textos. </t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="15" t="n"/>
-    </row>
-    <row r="20" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="B19" s="41" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="41" t="n"/>
+      <c r="G19" s="41" t="n"/>
+      <c r="H19" s="41" t="n"/>
+      <c r="I19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>III. JUSTIFICACIÓN DEL ESPACIO ACADÉMICO</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="66" customFormat="1" customHeight="1" s="31">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B20" s="41" t="n"/>
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="41" t="n"/>
+      <c r="G20" s="41" t="n"/>
+      <c r="H20" s="41" t="n"/>
+      <c r="I20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="66" customFormat="1" customHeight="1" s="2">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> La claridad comunicativa es una competencia transversal esencial para los profesionales técnicos. En campos como la ciencia, la ingeniería o la tecnología, la redacción de textos científicos y técnicos exige el dominio de estructuras, registros y criterios discursivos específicos. Esta asignatura refuerza las habilidades lingüísticas, argumentativas y estructurales para producir textos académicos y profesionales con rigor, sentido crítico y ética informacional, en escenarios de creciente digitalización, innovación e interdisciplina. </t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="14" t="n"/>
-      <c r="I21" s="15" t="n"/>
-    </row>
-    <row r="22" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="B21" s="41" t="n"/>
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="41" t="n"/>
+      <c r="G21" s="41" t="n"/>
+      <c r="H21" s="41" t="n"/>
+      <c r="I21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>IV. OBJETIVOS DEL ESPACIO ACADÉMICO (GENERAL Y ESPECÍFICOS)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="14" t="n"/>
-      <c r="I22" s="15" t="n"/>
-    </row>
-    <row r="23" ht="180" customFormat="1" customHeight="1" s="31">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B22" s="41" t="n"/>
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="180" customFormat="1" customHeight="1" s="2">
+      <c r="A23" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Objetivo General 
 Fortalecer en el estudiante las competencias comunicativas necesarias para la comprensión y producción de textos científicos, técnicos y argumentativos, mediante el análisis crítico, la apropiación de estructuras textuales y el uso ético de la información. 
@@ -1271,32 +1328,32 @@
 •	Fortalecer la argumentación escrita mediante distintos modos de razonamiento lógico y crítico. </t>
         </is>
       </c>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="14" t="n"/>
-      <c r="I23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="B23" s="41" t="n"/>
+      <c r="C23" s="41" t="n"/>
+      <c r="D23" s="41" t="n"/>
+      <c r="E23" s="41" t="n"/>
+      <c r="F23" s="41" t="n"/>
+      <c r="G23" s="41" t="n"/>
+      <c r="H23" s="41" t="n"/>
+      <c r="I23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">V. PROPÓSITOS DE FORMACIÓN Y DE APRENDIZAJE (PFA) DEL ESPACIO ACADÉMICO </t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-      <c r="I24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="193.5" customFormat="1" customHeight="1" s="31">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="B24" s="41" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="41" t="n"/>
+      <c r="E24" s="41" t="n"/>
+      <c r="F24" s="41" t="n"/>
+      <c r="G24" s="41" t="n"/>
+      <c r="H24" s="41" t="n"/>
+      <c r="I24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="193.5" customFormat="1" customHeight="1" s="2">
+      <c r="A25" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Propósitos de Formación 
 Desarrollar una conciencia crítica y ética sobre la producción y uso del conocimiento científico. 
@@ -1311,32 +1368,32 @@
 Adaptabilidad e innovación. </t>
         </is>
       </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="14" t="n"/>
-      <c r="H25" s="14" t="n"/>
-      <c r="I25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="41" t="n"/>
+      <c r="E25" s="41" t="n"/>
+      <c r="F25" s="41" t="n"/>
+      <c r="G25" s="41" t="n"/>
+      <c r="H25" s="41" t="n"/>
+      <c r="I25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>VI.  CONTENIDOS TEMÁTICOS</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="14" t="n"/>
-      <c r="H26" s="14" t="n"/>
-      <c r="I26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="409.6" customFormat="1" customHeight="1" s="31">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="41" t="n"/>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="41" t="n"/>
+      <c r="G26" s="41" t="n"/>
+      <c r="H26" s="41" t="n"/>
+      <c r="I26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="409.6" customFormat="1" customHeight="1" s="2">
+      <c r="A27" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Fundamentos para la producción de textos académicos (2 semanas) 
 •	¿Qué es escribir como científico? 
@@ -1369,73 +1426,73 @@
 •	Publicación en repositorio del aula. </t>
         </is>
       </c>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="23" t="n"/>
-    </row>
-    <row r="28" ht="55.5" customFormat="1" customHeight="1" s="31">
-      <c r="A28" s="26" t="n"/>
-      <c r="B28" s="34" t="n"/>
-      <c r="C28" s="34" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="27" t="n"/>
-    </row>
-    <row r="29" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="43" t="n"/>
+      <c r="E27" s="43" t="n"/>
+      <c r="F27" s="43" t="n"/>
+      <c r="G27" s="43" t="n"/>
+      <c r="H27" s="43" t="n"/>
+      <c r="I27" s="40" t="n"/>
+    </row>
+    <row r="28" ht="55.5" customFormat="1" customHeight="1" s="2">
+      <c r="A28" s="46" t="n"/>
+      <c r="B28" s="48" t="n"/>
+      <c r="C28" s="48" t="n"/>
+      <c r="D28" s="48" t="n"/>
+      <c r="E28" s="48" t="n"/>
+      <c r="F28" s="48" t="n"/>
+      <c r="G28" s="48" t="n"/>
+      <c r="H28" s="48" t="n"/>
+      <c r="I28" s="47" t="n"/>
+    </row>
+    <row r="29" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>VII. ESTRATEGIAS DE ENSEÑANZA QUE FAVORECEN EL APRENDIZAJE</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="15" t="n"/>
-    </row>
-    <row r="30" ht="57.75" customFormat="1" customHeight="1" s="31">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="B29" s="41" t="n"/>
+      <c r="C29" s="41" t="n"/>
+      <c r="D29" s="41" t="n"/>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="41" t="n"/>
+      <c r="G29" s="41" t="n"/>
+      <c r="H29" s="41" t="n"/>
+      <c r="I29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="57.75" customFormat="1" customHeight="1" s="2">
+      <c r="A30" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">La asignatura se desarrollará a través de talleres prácticos, análisis de modelos textuales, escritura guiada, debates argumentativos, corrección entre pares y proyectos finales. Se promoverá la autonomía, el uso de herramientas digitales para la producción textual y la participación activa en ejercicios de escritura académica. </t>
         </is>
       </c>
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="41" t="n"/>
+      <c r="D30" s="41" t="n"/>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="41" t="n"/>
+      <c r="G30" s="41" t="n"/>
+      <c r="H30" s="41" t="n"/>
+      <c r="I30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>VIII.  EVALUACIÓN</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="15" t="n"/>
-    </row>
-    <row r="32" ht="264.75" customFormat="1" customHeight="1" s="31">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="B31" s="41" t="n"/>
+      <c r="C31" s="41" t="n"/>
+      <c r="D31" s="41" t="n"/>
+      <c r="E31" s="41" t="n"/>
+      <c r="F31" s="41" t="n"/>
+      <c r="G31" s="41" t="n"/>
+      <c r="H31" s="41" t="n"/>
+      <c r="I31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="264.75" customFormat="1" customHeight="1" s="2">
+      <c r="A32" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> De acuerdo con el estatuto estudiantil vigente (Acuerdo No. 027 de 1993 expedido por el Consejo Superior Universitario y en su Artículo No. 42 y al Artículo No. 3, Literal d) el profesor al presentar el programa presenta una propuesta de evaluación como parte de su propuesta metodológica.  
 Para dar cumplimiento a lo dispuesto en el estatuto estudiantil, los porcentajes por corte se definen como se indica a continuación, con base en las fechas establecidos por el Consejo Académico en el respectivo calendario académico. 
@@ -1445,93 +1502,93 @@
 En todo caso, la evaluación será continua e integral, teniendo en cuenta los avances del estudiante en los siguientes aspectos: i) comprensión conceptual (pruebas escritas, talleres); ii) aplicación práctica (laboratorios, informes técnicos); iii) proyecto integrador final (análisis, diseño, montaje y presentación); y iv) participación y trabajo en equipo. Asimismo, se debe valorar el desarrollo de competencias comunicativas, resolución de problemas, uso de instrumentos, pensamiento lógico y creatividad. Las pruebas se concertarán con el grupo y se ajustarán a las fechas establecidas en el respectivo calendario académico </t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="B32" s="41" t="n"/>
+      <c r="C32" s="41" t="n"/>
+      <c r="D32" s="41" t="n"/>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="41" t="n"/>
+      <c r="G32" s="41" t="n"/>
+      <c r="H32" s="41" t="n"/>
+      <c r="I32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>IX. MEDIOS Y RECURSOS EDUCATIVOS</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="15" t="n"/>
-    </row>
-    <row r="34" ht="184.5" customFormat="1" customHeight="1" s="31">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="41" t="n"/>
+      <c r="D33" s="41" t="n"/>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="41" t="n"/>
+      <c r="G33" s="41" t="n"/>
+      <c r="H33" s="41" t="n"/>
+      <c r="I33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="184.5" customFormat="1" customHeight="1" s="2">
+      <c r="A34" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Para el adecuado desarrollo de este espacio académico, se requiere el uso de medios institucionales y recursos individuales que faciliten los procesos de enseñanza y aprendizaje, tanto en ambientes presenciales como virtuales. Las actividades teóricas se apoyarán en aulas de clase dotadas de medios audiovisuales (tablero, videobeam, sillas) y plataformas virtuales institucionales como Microsoft Teams o Google Meet. Además, será fundamental el acceso a presentaciones digitales, textos base, hojas de datos, artículos técnicos, bibliotecas y herramientas digitales (Google Docs, Canva, Moodle, Miro). Se fomentará el uso de gestores de referencias bibliográficas (Zotero, Mendeley). 
 Como recursos propios, el estudiante debe disponer de una calculadora científica, conexión estable a internet que la universidad proporciona, un sistema para la toma de apuntes (cuaderno, tablet o computador) y acceso a los materiales de clase. Será responsabilidad del estudiante descargar los insumos digitales y contar con los elementos necesarios que serán especificados previamente en cada práctica o proyecto. </t>
         </is>
       </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="B34" s="41" t="n"/>
+      <c r="C34" s="41" t="n"/>
+      <c r="D34" s="41" t="n"/>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="41" t="n"/>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="41" t="n"/>
+      <c r="I34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>X. PRÁCTICAS ACADÉMICAS - SALIDAS DE CAMPO</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="63.75" customFormat="1" customHeight="1" s="31">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="B35" s="41" t="n"/>
+      <c r="C35" s="41" t="n"/>
+      <c r="D35" s="41" t="n"/>
+      <c r="E35" s="41" t="n"/>
+      <c r="F35" s="41" t="n"/>
+      <c r="G35" s="41" t="n"/>
+      <c r="H35" s="41" t="n"/>
+      <c r="I35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="63.75" customFormat="1" customHeight="1" s="2">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Podrán incluirse actividades como observación de exposiciones científicas, conversatorios con investigadores, participación en ferias académicas, o análisis de informes técnicos reales de empresas o instituciones. Estas prácticas buscan acercar al estudiante a contextos reales de producción de conocimiento. </t>
         </is>
       </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
-      <c r="I36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="B36" s="41" t="n"/>
+      <c r="C36" s="41" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="41" t="n"/>
+      <c r="G36" s="41" t="n"/>
+      <c r="H36" s="41" t="n"/>
+      <c r="I36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>XI.  BIBLIOGRAFÍA</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n"/>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="15" t="n"/>
-    </row>
-    <row r="38" ht="72" customFormat="1" customHeight="1" s="31">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="B37" s="41" t="n"/>
+      <c r="C37" s="41" t="n"/>
+      <c r="D37" s="41" t="n"/>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="41" t="n"/>
+      <c r="G37" s="41" t="n"/>
+      <c r="H37" s="41" t="n"/>
+      <c r="I37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="72" customFormat="1" customHeight="1" s="2">
+      <c r="A38" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">•	Cassany, D. (2006). La cocina de la escritura. Anagrama. 
 •	Eco, U. (2001). Cómo se hace una tesis. Gedisa. 
@@ -1539,66 +1596,66 @@
 •	Swales, J. &amp; Feak, C. (2012). Academic Writing for Graduate Students. University of Michigan Press. </t>
         </is>
       </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="15" t="n"/>
-    </row>
-    <row r="39" ht="21.95" customFormat="1" customHeight="1" s="31">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="B38" s="41" t="n"/>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="41" t="n"/>
+      <c r="H38" s="41" t="n"/>
+      <c r="I38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="21.95" customFormat="1" customHeight="1" s="2">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>XII. SEGUIMIENTO Y ACTUALIZACIÓN DEL SYLLABUS</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="14" t="n"/>
-      <c r="G39" s="14" t="n"/>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="15" t="n"/>
-    </row>
-    <row r="40" customFormat="1" s="31">
-      <c r="A40" s="37" t="inlineStr">
+      <c r="B39" s="41" t="n"/>
+      <c r="C39" s="41" t="n"/>
+      <c r="D39" s="41" t="n"/>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="41" t="n"/>
+      <c r="G39" s="41" t="n"/>
+      <c r="H39" s="41" t="n"/>
+      <c r="I39" s="42" t="n"/>
+    </row>
+    <row r="40" customFormat="1" s="2">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Fecha revisión por Consejo Curricular:</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="14" t="n"/>
-      <c r="G40" s="14" t="n"/>
-      <c r="H40" s="14" t="n"/>
-      <c r="I40" s="15" t="n"/>
-    </row>
-    <row r="41" ht="30" customFormat="1" customHeight="1" s="31">
+      <c r="B40" s="41" t="n"/>
+      <c r="C40" s="42" t="n"/>
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="41" t="n"/>
+      <c r="G40" s="41" t="n"/>
+      <c r="H40" s="41" t="n"/>
+      <c r="I40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="30" customFormat="1" customHeight="1" s="2">
       <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Fecha aprobación por Consejo Curricular:</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="15" t="n"/>
-      <c r="G41" s="40" t="inlineStr">
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="42" t="n"/>
+      <c r="G41" s="22" t="inlineStr">
         <is>
           <t>Número de acta:</t>
         </is>
       </c>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="15" t="n"/>
-    </row>
-    <row r="42" ht="6" customFormat="1" customHeight="1" s="31">
-      <c r="A42" s="30" t="n"/>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="6" customFormat="1" customHeight="1" s="2">
+      <c r="A42" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -1612,9 +1669,9 @@
     <mergeCell ref="E9:G9"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="H9:I9"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="A33:I33"/>
@@ -1622,8 +1679,8 @@
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="G1:I3"/>
-    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A22:I22"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
@@ -919,7 +919,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-22/02/2025</t>
+01/01/2000</t>
         </is>
       </c>
       <c r="G3" s="46" t="n"/>

--- a/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
+++ b/Syllabus_Electronica/Tecnología en Electrónica Industrial/Área Complementaria/Lenguaje/1056 - Producción y Comprensión de Textos II.xlsx
@@ -919,7 +919,7 @@
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Fecha de Aprobación:
-01/01/2000</t>
+10/10/2000</t>
         </is>
       </c>
       <c r="G3" s="46" t="n"/>
